--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-document-attache.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-document-attache.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4337" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4337" uniqueCount="464">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1338,6 +1338,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Organizer.component:frObservationMedia.observationMedia.subject</t>
@@ -14334,7 +14338,7 @@
         <v>74</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>74</v>
+        <v>427</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>74</v>
@@ -14342,10 +14346,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14421,7 +14425,7 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -14441,10 +14445,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14520,7 +14524,7 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -14540,10 +14544,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14619,7 +14623,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -14639,10 +14643,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14718,7 +14722,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -14738,10 +14742,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14817,7 +14821,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -14837,10 +14841,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14916,7 +14920,7 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -14936,10 +14940,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -14962,7 +14966,7 @@
         <v>74</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L131" s="2"/>
       <c r="M131" s="2"/>
@@ -15015,7 +15019,7 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -15035,10 +15039,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15114,7 +15118,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -15134,10 +15138,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15213,7 +15217,7 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -15233,10 +15237,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15312,7 +15316,7 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -15332,7 +15336,7 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>291</v>
@@ -15431,7 +15435,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>295</v>
@@ -15530,7 +15534,7 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>299</v>
@@ -15629,7 +15633,7 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B138" t="s" s="2">
         <v>303</v>
@@ -15728,7 +15732,7 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B139" t="s" s="2">
         <v>307</v>
